--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260701.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260701.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.28%</t>
+          <t>10.24%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.11%</t>
+          <t>10.24%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.99%</t>
+          <t>5.80%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>5.08%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.39%</t>
+          <t>4.13%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.52%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.48%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -814,117 +814,117 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>28,430,000</t>
+          <t>25,824,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>25,824,000</t>
+          <t>1,872</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>1,872</t>
+          <t>28,430,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>134,019,945</t>
+          <t>30,666,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>30,666,000</t>
+          <t>134,019,945</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
@@ -953,44 +953,44 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>145,692,000</t>
+          <t>130,597,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>130,597,000</t>
+          <t>145,692,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
@@ -1063,44 +1063,44 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>364,675,000</t>
+          <t>62,290,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>62,290,000</t>
+          <t>364,675,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
@@ -1166,68 +1166,68 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>51,717,000</t>
+          <t>14,343,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>33,450,000</t>
+          <t>51,717,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14,343,000</t>
+          <t>33,450,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>4,635,619,240</t>
+          <t>10,818,453,885</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>11,054,588,296</t>
+          <t>7,220,073,096</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-383,754,106</t>
+          <t>-450,375,379</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
